--- a/Vendor_Scope_Fit_Matrix_1.0.xlsx
+++ b/Vendor_Scope_Fit_Matrix_1.0.xlsx
@@ -424,7 +424,7 @@
         <v>Scope名称</v>
       </c>
       <c r="B2" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -440,7 +440,7 @@
         <v>Scope类别</v>
       </c>
       <c r="B4" t="str">
-        <v>MECH</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -457,13 +457,13 @@
         <v>评分标准（1-5）</v>
       </c>
       <c r="E6" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="F6" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="G6" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="H6" t="str">
         <v>加权得分 A</v>
@@ -488,23 +488,23 @@
       <c r="D7" t="str">
         <v>1=无经验；3=部分经验；5=大量成熟案例</v>
       </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -520,23 +520,23 @@
       <c r="D8" t="str">
         <v>1=不适合；3=部分适合；5=高度适合</v>
       </c>
-      <c r="E8">
-        <v>5</v>
-      </c>
-      <c r="F8">
-        <v>5</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -552,23 +552,23 @@
       <c r="D9" t="str">
         <v>1=风险较高；3=基本可交付；5=成熟稳定</v>
       </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <v>1.25</v>
-      </c>
-      <c r="I9">
-        <v>1.25</v>
-      </c>
-      <c r="J9">
-        <v>1.25</v>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -584,23 +584,23 @@
       <c r="D10" t="str">
         <v>1=团队风险高；3=基本满足；5=团队成熟稳定</v>
       </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -616,23 +616,23 @@
       <c r="D11" t="str">
         <v>1=关系较弱；3=基本合作；5=深度战略合作</v>
       </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="F11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>0.75</v>
-      </c>
-      <c r="I11">
-        <v>0.75</v>
-      </c>
-      <c r="J11">
-        <v>0.75</v>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -649,13 +649,13 @@
         <v>Scope Fit %</v>
       </c>
       <c r="E13" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="F13" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="G13" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
     </row>
     <row r="15">
@@ -700,7 +700,7 @@
         <v>导出时间</v>
       </c>
       <c r="B21" t="str">
-        <v>2026/5/19 10:38:08</v>
+        <v>2026/5/19 10:45:51</v>
       </c>
     </row>
   </sheetData>
@@ -752,10 +752,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="B2" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C2" t="str">
         <v>类似经验</v>
@@ -763,8 +763,8 @@
       <c r="D2">
         <v>20</v>
       </c>
-      <c r="E2">
-        <v>5</v>
+      <c r="E2" t="str">
+        <v/>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="B3" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C3" t="str">
         <v>是否适合我们的运营环境</v>
@@ -789,8 +789,8 @@
       <c r="D3">
         <v>20</v>
       </c>
-      <c r="E3">
-        <v>5</v>
+      <c r="E3" t="str">
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -804,10 +804,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="B4" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C4" t="str">
         <v>稳定交付能力</v>
@@ -815,8 +815,8 @@
       <c r="D4">
         <v>25</v>
       </c>
-      <c r="E4">
-        <v>5</v>
+      <c r="E4" t="str">
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -830,10 +830,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="B5" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C5" t="str">
         <v>团队构成</v>
@@ -841,8 +841,8 @@
       <c r="D5">
         <v>20</v>
       </c>
-      <c r="E5">
-        <v>5</v>
+      <c r="E5" t="str">
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -856,10 +856,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="B6" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C6" t="str">
         <v>OEM供应商关系</v>
@@ -867,8 +867,8 @@
       <c r="D6">
         <v>15</v>
       </c>
-      <c r="E6">
-        <v>5</v>
+      <c r="E6" t="str">
+        <v/>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -882,10 +882,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="B7" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C7" t="str">
         <v>类似经验</v>
@@ -893,8 +893,8 @@
       <c r="D7">
         <v>20</v>
       </c>
-      <c r="E7">
-        <v>5</v>
+      <c r="E7" t="str">
+        <v/>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -908,10 +908,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="B8" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C8" t="str">
         <v>是否适合我们的运营环境</v>
@@ -919,8 +919,8 @@
       <c r="D8">
         <v>20</v>
       </c>
-      <c r="E8">
-        <v>5</v>
+      <c r="E8" t="str">
+        <v/>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -934,10 +934,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="B9" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C9" t="str">
         <v>稳定交付能力</v>
@@ -945,8 +945,8 @@
       <c r="D9">
         <v>25</v>
       </c>
-      <c r="E9">
-        <v>5</v>
+      <c r="E9" t="str">
+        <v/>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -960,10 +960,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="B10" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C10" t="str">
         <v>团队构成</v>
@@ -971,8 +971,8 @@
       <c r="D10">
         <v>20</v>
       </c>
-      <c r="E10">
-        <v>5</v>
+      <c r="E10" t="str">
+        <v/>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -986,10 +986,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="B11" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C11" t="str">
         <v>OEM供应商关系</v>
@@ -997,25 +997,25 @@
       <c r="D11">
         <v>15</v>
       </c>
-      <c r="E11">
-        <v>5</v>
+      <c r="E11" t="str">
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>基于经验</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>基于经验</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>基于经验</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="B12" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C12" t="str">
         <v>类似经验</v>
@@ -1023,8 +1023,8 @@
       <c r="D12">
         <v>20</v>
       </c>
-      <c r="E12">
-        <v>5</v>
+      <c r="E12" t="str">
+        <v/>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="B13" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C13" t="str">
         <v>是否适合我们的运营环境</v>
@@ -1049,8 +1049,8 @@
       <c r="D13">
         <v>20</v>
       </c>
-      <c r="E13">
-        <v>5</v>
+      <c r="E13" t="str">
+        <v/>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="B14" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C14" t="str">
         <v>稳定交付能力</v>
@@ -1075,8 +1075,8 @@
       <c r="D14">
         <v>25</v>
       </c>
-      <c r="E14">
-        <v>5</v>
+      <c r="E14" t="str">
+        <v/>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -1090,10 +1090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="B15" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C15" t="str">
         <v>团队构成</v>
@@ -1101,8 +1101,8 @@
       <c r="D15">
         <v>20</v>
       </c>
-      <c r="E15">
-        <v>5</v>
+      <c r="E15" t="str">
+        <v/>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="B16" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="C16" t="str">
         <v>OEM供应商关系</v>
@@ -1127,8 +1127,8 @@
       <c r="D16">
         <v>15</v>
       </c>
-      <c r="E16">
-        <v>5</v>
+      <c r="E16" t="str">
+        <v/>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1197,13 +1197,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>MECH</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="D2" t="str">
         <v>L3</v>
@@ -1215,10 +1215,10 @@
         <v>进行中 In Progress</v>
       </c>
       <c r="G2" t="str">
-        <v>JCI</v>
+        <v>Vendor A</v>
       </c>
       <c r="H2" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="B3" t="str">
-        <v>MECH</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v>L3</v>
@@ -1247,10 +1247,10 @@
         <v>进行中 In Progress</v>
       </c>
       <c r="G3" t="str">
-        <v>YM</v>
+        <v>Vendor B</v>
       </c>
       <c r="H3" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -1261,13 +1261,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>MECH</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>燃油系统</v>
+        <v/>
       </c>
       <c r="D4" t="str">
         <v>L3</v>
@@ -1279,10 +1279,10 @@
         <v>进行中 In Progress</v>
       </c>
       <c r="G4" t="str">
-        <v>ECI</v>
+        <v>Vendor C</v>
       </c>
       <c r="H4" t="str">
-        <v>100%</v>
+        <v>0%</v>
       </c>
       <c r="I4" t="str">
         <v/>
